--- a/Excel/AbyssCopyConfig.xlsx
+++ b/Excel/AbyssCopyConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="26">
   <si>
     <t>#</t>
   </si>
@@ -43,15 +43,15 @@
     <t>Id</t>
   </si>
   <si>
+    <t>Stage</t>
+  </si>
+  <si>
     <t>Cycle</t>
   </si>
   <si>
     <t>MapName</t>
   </si>
   <si>
-    <t>MonsterName</t>
-  </si>
-  <si>
     <t>Attr</t>
   </si>
   <si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>深渊战场一层</t>
-  </si>
-  <si>
-    <t>张角</t>
   </si>
   <si>
     <t>深渊战场二层</t>
@@ -1078,14 +1075,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
-    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.3333333333333" style="1" customWidth="1"/>
+    <col min="3" max="5" width="9.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.625" style="3" customWidth="1"/>
     <col min="8" max="8" width="17" style="3" customWidth="1"/>
     <col min="9" max="9" width="19.25" style="3" customWidth="1"/>
@@ -1226,7 +1222,7 @@
         <v>14</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>15</v>
@@ -1266,23 +1262,23 @@
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="G6" s="7">
-        <f t="shared" ref="G6:G15" si="0">Q6*20000000</f>
-        <v>20000000</v>
+        <f t="shared" ref="G6:G13" si="0">Q6*2000000</f>
+        <v>2000000</v>
       </c>
       <c r="H6" s="7">
-        <f t="shared" ref="H6:H15" si="1">Q6*20000000</f>
-        <v>20000000</v>
+        <f t="shared" ref="H6:H13" si="1">Q6*5000000</f>
+        <v>5000000</v>
       </c>
       <c r="I6" s="7">
-        <f t="shared" ref="I6:I15" si="2">Q6*200000000000</f>
-        <v>200000000000</v>
+        <f t="shared" ref="I6:I13" si="2">Q6*50000000000</f>
+        <v>50000000000</v>
       </c>
       <c r="J6" s="7">
         <v>100</v>
@@ -1311,25 +1307,25 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
         <v>1</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="7">
         <f t="shared" si="0"/>
-        <v>40000000</v>
+        <v>4000000</v>
       </c>
       <c r="H7" s="7">
         <f t="shared" si="1"/>
-        <v>40000000</v>
+        <v>10000000</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" si="2"/>
-        <v>400000000000</v>
+        <v>100000000000</v>
       </c>
       <c r="J7" s="7">
         <v>100</v>
@@ -1358,25 +1354,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G8" s="7">
         <f t="shared" si="0"/>
-        <v>60000000</v>
+        <v>8000000</v>
       </c>
       <c r="H8" s="7">
         <f t="shared" si="1"/>
-        <v>60000000</v>
+        <v>20000000</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" si="2"/>
-        <v>600000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="J8" s="7">
         <v>100</v>
@@ -1397,7 +1393,7 @@
         <v>99</v>
       </c>
       <c r="Q8" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:17">
@@ -1405,25 +1401,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="1">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G9" s="7">
         <f t="shared" si="0"/>
-        <v>80000000</v>
+        <v>16000000</v>
       </c>
       <c r="H9" s="7">
         <f t="shared" si="1"/>
-        <v>80000000</v>
+        <v>40000000</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" si="2"/>
-        <v>800000000000</v>
+        <v>400000000000</v>
       </c>
       <c r="J9" s="7">
         <v>100</v>
@@ -1444,7 +1440,7 @@
         <v>99</v>
       </c>
       <c r="Q9" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:17">
@@ -1452,25 +1448,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="1">
+        <v>5</v>
+      </c>
+      <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G10" s="7">
         <f t="shared" si="0"/>
-        <v>100000000</v>
+        <v>32000000</v>
       </c>
       <c r="H10" s="7">
         <f t="shared" si="1"/>
-        <v>100000000</v>
+        <v>80000000</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" si="2"/>
-        <v>1000000000000</v>
+        <v>800000000000</v>
       </c>
       <c r="J10" s="7">
         <v>100</v>
@@ -1491,7 +1487,7 @@
         <v>99</v>
       </c>
       <c r="Q10" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:17">
@@ -1499,25 +1495,25 @@
         <v>6</v>
       </c>
       <c r="D11" s="1">
+        <v>6</v>
+      </c>
+      <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G11" s="7">
         <f t="shared" si="0"/>
-        <v>120000000</v>
+        <v>64000000</v>
       </c>
       <c r="H11" s="7">
         <f t="shared" si="1"/>
-        <v>120000000</v>
+        <v>160000000</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" si="2"/>
-        <v>1200000000000</v>
+        <v>1600000000000</v>
       </c>
       <c r="J11" s="7">
         <v>100</v>
@@ -1538,7 +1534,7 @@
         <v>99</v>
       </c>
       <c r="Q11" s="2">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:17">
@@ -1546,25 +1542,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="1">
+        <v>7</v>
+      </c>
+      <c r="E12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F12" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G12" s="7">
         <f t="shared" si="0"/>
-        <v>140000000</v>
+        <v>128000000</v>
       </c>
       <c r="H12" s="7">
         <f t="shared" si="1"/>
-        <v>140000000</v>
+        <v>320000000</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" si="2"/>
-        <v>1400000000000</v>
+        <v>3200000000000</v>
       </c>
       <c r="J12" s="7">
         <v>100</v>
@@ -1585,7 +1581,7 @@
         <v>99</v>
       </c>
       <c r="Q12" s="2">
-        <v>7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:17">
@@ -1593,25 +1589,25 @@
         <v>8</v>
       </c>
       <c r="D13" s="1">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G13" s="7">
         <f t="shared" si="0"/>
-        <v>160000000</v>
+        <v>256000000</v>
       </c>
       <c r="H13" s="7">
         <f t="shared" si="1"/>
-        <v>160000000</v>
+        <v>640000000</v>
       </c>
       <c r="I13" s="7">
         <f t="shared" si="2"/>
-        <v>1600000000000</v>
+        <v>6400000000000</v>
       </c>
       <c r="J13" s="7">
         <v>100</v>
@@ -1632,33 +1628,39 @@
         <v>99</v>
       </c>
       <c r="Q13" s="2">
-        <v>8</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:17">
+      <c r="A14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G14" s="7">
-        <f t="shared" si="0"/>
-        <v>180000000</v>
+        <f>Q14*800000</f>
+        <v>204800000</v>
       </c>
       <c r="H14" s="7">
-        <f t="shared" si="1"/>
-        <v>180000000</v>
+        <f>Q14*2000000</f>
+        <v>512000000</v>
       </c>
       <c r="I14" s="7">
-        <f t="shared" si="2"/>
-        <v>1800000000000</v>
+        <f>Q14*20000000000</f>
+        <v>5120000000000</v>
       </c>
       <c r="J14" s="7">
         <v>100</v>
@@ -1679,33 +1681,39 @@
         <v>99</v>
       </c>
       <c r="Q14" s="2">
-        <v>9</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:17">
+      <c r="A15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1">
         <v>1</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G15" s="7">
-        <f t="shared" si="0"/>
-        <v>200000000</v>
+        <f>Q15*800000</f>
+        <v>409600000</v>
       </c>
       <c r="H15" s="7">
-        <f t="shared" si="1"/>
-        <v>200000000</v>
+        <f>Q15*2000000</f>
+        <v>1024000000</v>
       </c>
       <c r="I15" s="7">
-        <f t="shared" si="2"/>
-        <v>2000000000000</v>
+        <f>Q15*20000000000</f>
+        <v>10240000000000</v>
       </c>
       <c r="J15" s="7">
         <v>100</v>
@@ -1726,7 +1734,7 @@
         <v>99</v>
       </c>
       <c r="Q15" s="2">
-        <v>10</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:17">
@@ -1745,9 +1753,12 @@
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
     </row>
+    <row r="21" customHeight="1" spans="7:8">
+      <c r="G21" s="7"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5 G3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:O5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
